--- a/Spotify_Audiobooks_Regional_Access.xlsx
+++ b/Spotify_Audiobooks_Regional_Access.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Data_User_Inputs" sheetId="4" r:id="rId4"/>
     <sheet name="Calcs_Audiobook_Access" sheetId="5" r:id="rId5"/>
     <sheet name="Summary" sheetId="6" r:id="rId6"/>
+    <sheet name="SPP" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -52,28 +53,6 @@
   </fills>
   <borders count="9">
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -81,15 +60,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -108,6 +78,37 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -123,19 +124,19 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color indexed="64"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -590,84 +591,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Field</t>
         </is>
       </c>
-      <c r="B1" s="54" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Spotify Audiobooks — Regional Availability &amp; Premium User Access</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Ticker</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">SPOT</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">As Of</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Subject</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook market availability by region</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Analyst</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Research</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Created</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
@@ -689,39 +690,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Market</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Live (Pre-Oct 2026)</t>
         </is>
       </c>
-      <c r="D1" s="26" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Launch Date</t>
         </is>
       </c>
-      <c r="E1" s="26" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Access Model</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Rollout By YE2026</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">North America</t>
         </is>
@@ -746,14 +747,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">North America</t>
         </is>
@@ -778,14 +779,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -810,14 +811,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -842,14 +843,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -874,14 +875,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -906,14 +907,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -938,14 +939,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -970,14 +971,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1002,14 +1003,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1034,14 +1035,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1066,14 +1067,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1098,14 +1099,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1130,14 +1131,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1162,14 +1163,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1194,14 +1195,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1226,14 +1227,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1258,14 +1259,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1290,14 +1291,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1322,14 +1323,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1354,14 +1355,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1386,14 +1387,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -1418,14 +1419,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Emerging Europe</t>
         </is>
@@ -1450,14 +1451,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -1482,14 +1483,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -1514,14 +1515,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -1546,14 +1547,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -1578,14 +1579,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -1610,14 +1611,14 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -1642,14 +1643,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia</t>
         </is>
@@ -1674,14 +1675,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia</t>
         </is>
@@ -1706,14 +1707,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia</t>
         </is>
@@ -1738,14 +1739,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia</t>
         </is>
@@ -1770,14 +1771,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Southeast Asia</t>
         </is>
@@ -1802,14 +1803,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Middle East</t>
         </is>
@@ -1834,14 +1835,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Africa</t>
         </is>
@@ -1866,14 +1867,14 @@
           <t xml:space="preserve">Audiobooks+ (add-on)</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Australasia</t>
         </is>
@@ -1898,39 +1899,39 @@
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Australasia</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">New Zealand</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-10-03</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes</t>
         </is>
@@ -1950,29 +1951,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Figure</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Value</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">As_Of</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobooks live in 22 markets; expanding to 180+ by end of 2026</t>
         </is>
@@ -1987,14 +1988,14 @@
           <t xml:space="preserve">Spotify Newsroom: 'Audiobooks on Spotify Are Going Global'</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Rollout timing: 'from now through the end of 2026'</t>
         </is>
@@ -2009,14 +2010,14 @@
           <t xml:space="preserve">Spotify Newsroom press release; TechCrunch same-day ('starts today, continues over coming months')</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">US, Canada, UK, Ireland, Australia, NZ launch (included hours)</t>
         </is>
@@ -2031,14 +2032,14 @@
           <t xml:space="preserve">Spotify Newsroom: 'Audiobooks included in Spotify Premium'</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-10-03</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">France, Belgium, Netherlands, Luxembourg launch</t>
         </is>
@@ -2053,14 +2054,14 @@
           <t xml:space="preserve">Spotify Newsroom launch post</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-10-14</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Germany, Austria, Switzerland, Liechtenstein launch</t>
         </is>
@@ -2075,14 +2076,14 @@
           <t xml:space="preserve">Spotify Newsroom</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-15</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sweden, Denmark, Finland, Iceland, Monaco launch</t>
         </is>
@@ -2097,14 +2098,14 @@
           <t xml:space="preserve">Spotify Newsroom</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-18</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobooks in Premium (12 hrs/mo) named markets</t>
         </is>
@@ -2119,14 +2120,14 @@
           <t xml:space="preserve">Spotify Newsroom press release</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobooks+ (paid add-on) primary model</t>
         </is>
@@ -2141,14 +2142,14 @@
           <t xml:space="preserve">Spotify Newsroom press release</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">India rollout date (press-reported, not confirmed by Spotify primary)</t>
         </is>
@@ -2163,14 +2164,14 @@
           <t xml:space="preserve">Economic Times / Times of India</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">global Premium subscribers</t>
         </is>
@@ -2185,14 +2186,14 @@
           <t xml:space="preserve">Spotify Q2 2026 Shareholder Deck, investors.spotify.com</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Premium users by region</t>
         </is>
@@ -2207,14 +2208,14 @@
           <t xml:space="preserve">Q2 2026 Shareholder Deck reports global totals only, no regional split</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Premium users per region (North America 73.3M, Developed Europe 96.9M, etc.)</t>
         </is>
@@ -2229,14 +2230,14 @@
           <t xml:space="preserve">Provided by user; not a Spotify disclosure - unverifiable</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Addressable population per region</t>
         </is>
@@ -2251,29 +2252,29 @@
           <t xml:space="preserve">Provided by user (estimate of people who could use/afford Premium)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Live / YE2026 coverage % by region</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Analyst estimate from market mapping</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Derived: regions weighted by whether named markets are live vs rolling</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
@@ -2294,34 +2295,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="B1" s="107" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Premium Users (M)</t>
         </is>
       </c>
-      <c r="C1" s="107" t="inlineStr">
+      <c r="C1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Addressable Population (M)</t>
         </is>
       </c>
-      <c r="D1" s="143" t="inlineStr">
+      <c r="D1" s="142" t="inlineStr">
         <is>
           <t xml:space="preserve">Live Audiobook Coverage (% of users)</t>
         </is>
       </c>
-      <c r="E1" s="135" t="inlineStr">
+      <c r="E1" s="138" t="inlineStr">
         <is>
           <t xml:space="preserve">YE2026 Audiobook Coverage (% of users)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">North America</t>
         </is>
@@ -2335,12 +2336,12 @@
       <c r="D2" s="123">
         <v>1</v>
       </c>
-      <c r="E2" s="120">
+      <c r="E2" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -2354,12 +2355,12 @@
       <c r="D3" s="123">
         <v>0.85</v>
       </c>
-      <c r="E3" s="120">
+      <c r="E3" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Emerging Europe</t>
         </is>
@@ -2373,12 +2374,12 @@
       <c r="D4" s="123">
         <v>0</v>
       </c>
-      <c r="E4" s="120">
+      <c r="E4" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -2392,12 +2393,12 @@
       <c r="D5" s="123">
         <v>0</v>
       </c>
-      <c r="E5" s="120">
+      <c r="E5" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia</t>
         </is>
@@ -2411,12 +2412,12 @@
       <c r="D6" s="123">
         <v>0</v>
       </c>
-      <c r="E6" s="120">
+      <c r="E6" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Southeast Asia</t>
         </is>
@@ -2430,12 +2431,12 @@
       <c r="D7" s="123">
         <v>0</v>
       </c>
-      <c r="E7" s="120">
+      <c r="E7" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Middle East</t>
         </is>
@@ -2449,12 +2450,12 @@
       <c r="D8" s="123">
         <v>0</v>
       </c>
-      <c r="E8" s="120">
+      <c r="E8" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Africa</t>
         </is>
@@ -2468,12 +2469,12 @@
       <c r="D9" s="123">
         <v>0</v>
       </c>
-      <c r="E9" s="120">
+      <c r="E9" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Australasia</t>
         </is>
@@ -2487,24 +2488,24 @@
       <c r="D10" s="123">
         <v>1</v>
       </c>
-      <c r="E10" s="120">
+      <c r="E10" s="119">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="B11" s="88">
+      <c r="B11" s="89">
         <v>293.2</v>
       </c>
-      <c r="C11" s="88">
+      <c r="C11" s="89">
         <v>2988</v>
       </c>
-      <c r="D11" s="124"/>
-      <c r="E11" s="122"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="121"/>
     </row>
   </sheetData>
 </worksheet>
@@ -2522,39 +2523,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Region</t>
         </is>
       </c>
-      <c r="B1" s="107" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Premium Users (M)</t>
         </is>
       </c>
-      <c r="C1" s="143" t="inlineStr">
+      <c r="C1" s="142" t="inlineStr">
         <is>
           <t xml:space="preserve">Live Coverage (%)</t>
         </is>
       </c>
-      <c r="D1" s="107" t="inlineStr">
+      <c r="D1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Access Now (M)</t>
         </is>
       </c>
-      <c r="E1" s="143" t="inlineStr">
+      <c r="E1" s="142" t="inlineStr">
         <is>
           <t xml:space="preserve">YE2026 Coverage (%)</t>
         </is>
       </c>
-      <c r="F1" s="99" t="inlineStr">
+      <c r="F1" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Access By YE2026 (M)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">North America</t>
         </is>
@@ -2571,12 +2572,12 @@
       <c r="E2" s="123">
         <v>1</v>
       </c>
-      <c r="F2" s="84">
+      <c r="F2" s="83">
         <v>73.3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Developed Europe</t>
         </is>
@@ -2593,12 +2594,12 @@
       <c r="E3" s="123">
         <v>1</v>
       </c>
-      <c r="F3" s="84">
+      <c r="F3" s="83">
         <v>96.9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Emerging Europe</t>
         </is>
@@ -2615,12 +2616,12 @@
       <c r="E4" s="123">
         <v>1</v>
       </c>
-      <c r="F4" s="84">
+      <c r="F4" s="83">
         <v>8.6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -2637,12 +2638,12 @@
       <c r="E5" s="123">
         <v>1</v>
       </c>
-      <c r="F5" s="84">
+      <c r="F5" s="83">
         <v>70.3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia</t>
         </is>
@@ -2659,12 +2660,12 @@
       <c r="E6" s="123">
         <v>1</v>
       </c>
-      <c r="F6" s="84">
+      <c r="F6" s="83">
         <v>6.9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Southeast Asia</t>
         </is>
@@ -2681,12 +2682,12 @@
       <c r="E7" s="123">
         <v>1</v>
       </c>
-      <c r="F7" s="84">
+      <c r="F7" s="83">
         <v>6.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Middle East</t>
         </is>
@@ -2703,12 +2704,12 @@
       <c r="E8" s="123">
         <v>1</v>
       </c>
-      <c r="F8" s="84">
+      <c r="F8" s="83">
         <v>1.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Africa</t>
         </is>
@@ -2725,12 +2726,12 @@
       <c r="E9" s="123">
         <v>1</v>
       </c>
-      <c r="F9" s="84">
+      <c r="F9" s="83">
         <v>24.2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Australasia</t>
         </is>
@@ -2747,23 +2748,23 @@
       <c r="E10" s="123">
         <v>1</v>
       </c>
-      <c r="F10" s="84">
+      <c r="F10" s="83">
         <v>5.3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="B11" s="88">
+      <c r="B11" s="89">
         <v>293.2</v>
       </c>
-      <c r="C11" s="124">
+      <c r="C11" s="125">
         <v>160.965</v>
       </c>
-      <c r="D11" s="88">
+      <c r="D11" s="89">
         <v>293.2</v>
       </c>
     </row>
@@ -2788,64 +2789,64 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Region / Country</t>
         </is>
       </c>
-      <c r="B1" s="107" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Addressable Population (M)</t>
         </is>
       </c>
-      <c r="C1" s="107" t="inlineStr">
+      <c r="C1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Premium Users (M)</t>
         </is>
       </c>
-      <c r="D1" s="107" t="inlineStr">
+      <c r="D1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Access Now (M)</t>
         </is>
       </c>
-      <c r="E1" s="143" t="inlineStr">
+      <c r="E1" s="142" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Access Now (% of users)</t>
         </is>
       </c>
-      <c r="F1" s="107" t="inlineStr">
+      <c r="F1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Access By YE2026 (M)</t>
         </is>
       </c>
-      <c r="G1" s="143" t="inlineStr">
+      <c r="G1" s="142" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Access By YE2026 (% of users)</t>
         </is>
       </c>
-      <c r="H1" s="35" t="inlineStr">
+      <c r="H1" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">First Audiobook Access</t>
         </is>
       </c>
-      <c r="I1" s="35" t="inlineStr">
+      <c r="I1" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">First Monetization (Included/Paid)</t>
         </is>
       </c>
-      <c r="J1" s="107" t="inlineStr">
+      <c r="J1" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">Months to Monetization</t>
         </is>
       </c>
-      <c r="K1" s="27" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">Access Model</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">United States</t>
         </is>
@@ -2881,14 +2882,14 @@
       <c r="J2" s="87">
         <v>14</v>
       </c>
-      <c r="K2" s="12" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours / Audiobooks+</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Canada</t>
         </is>
@@ -2924,14 +2925,14 @@
       <c r="J3" s="87">
         <v>13</v>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours / Audiobooks+</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">United Kingdom</t>
         </is>
@@ -2967,14 +2968,14 @@
       <c r="J4" s="87">
         <v>11</v>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours / Audiobooks+</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Germany</t>
         </is>
@@ -3010,14 +3011,14 @@
       <c r="J5" s="87">
         <v>0</v>
       </c>
-      <c r="K5" s="12" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours / Audiobooks+</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">France</t>
         </is>
@@ -3053,14 +3054,14 @@
       <c r="J6" s="87">
         <v>0</v>
       </c>
-      <c r="K6" s="12" t="inlineStr">
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours / Audiobooks+</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Netherlands</t>
         </is>
@@ -3096,14 +3097,14 @@
       <c r="J7" s="87">
         <v>0</v>
       </c>
-      <c r="K7" s="12" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours / Audiobooks+</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Sweden</t>
         </is>
@@ -3139,14 +3140,14 @@
       <c r="J8" s="87">
         <v>0</v>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours / Audiobooks+</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Remaining Developed Europe</t>
         </is>
@@ -3170,16 +3171,9 @@
         <v>1</v>
       </c>
       <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Included hours / Audiobooks+</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Australia</t>
         </is>
@@ -3215,14 +3209,14 @@
       <c r="J10" s="87">
         <v>11</v>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Included hours / Audiobooks+</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Emerging Europe</t>
         </is>
@@ -3246,16 +3240,9 @@
         <v>1</v>
       </c>
       <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="87"/>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audiobooks+ only</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America</t>
         </is>
@@ -3279,16 +3266,9 @@
         <v>1</v>
       </c>
       <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="87"/>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Included hours / Audiobooks+ (BR/MX/CO/CL/PE) ; Audiobooks+ only (AR)</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Asia</t>
         </is>
@@ -3312,16 +3292,9 @@
         <v>1</v>
       </c>
       <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audiobooks+ only</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Southeast Asia</t>
         </is>
@@ -3345,16 +3318,9 @@
         <v>1</v>
       </c>
       <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audiobooks+ only</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Middle East</t>
         </is>
@@ -3378,16 +3344,9 @@
         <v>1</v>
       </c>
       <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audiobooks+ only</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">Africa</t>
         </is>
@@ -3411,42 +3370,2047 @@
         <v>1</v>
       </c>
       <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audiobooks+ only</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="B17" s="88">
+      <c r="B17" s="89">
         <v>2988</v>
       </c>
-      <c r="C17" s="88">
+      <c r="C17" s="89">
         <v>293.2</v>
       </c>
-      <c r="D17" s="88">
+      <c r="D17" s="89">
         <v>162</v>
       </c>
-      <c r="E17" s="124">
+      <c r="E17" s="125">
         <v>0.552</v>
       </c>
-      <c r="F17" s="88">
+      <c r="F17" s="89">
         <v>293.2</v>
       </c>
-      <c r="G17" s="124">
+      <c r="G17" s="125">
         <v>1</v>
       </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="14"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="13"/>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="18.00" customWidth="1"/>
+    <col min="2" max="2" width="34.00" customWidth="1"/>
+    <col min="3" max="3" width="24.00" customWidth="1"/>
+    <col min="4" max="4" width="14.00" customWidth="1"/>
+    <col min="5" max="5" width="14.00" customWidth="1"/>
+    <col min="6" max="6" width="42.00" customWidth="1"/>
+    <col min="7" max="7" width="16.00" customWidth="1"/>
+    <col min="8" max="8" width="22.00" customWidth="1"/>
+    <col min="9" max="9" width="40.00" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Region</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Market</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPP Status</t>
+        </is>
+      </c>
+      <c r="D1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPP Live Date</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local Ad Delivery by Spotify</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Creators Can Earn</t>
+        </is>
+      </c>
+      <c r="G1" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Premium Users (M)</t>
+        </is>
+      </c>
+      <c r="H1" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Addressable Population (M)</t>
+        </is>
+      </c>
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North America</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-02</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G2" s="78"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North America</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canada</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-02</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G3" s="78"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United Kingdom</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-02</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G4" s="78"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ireland</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G5" s="78"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G6" s="78"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belgium</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G7" s="78"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Netherlands</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G8" s="78"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luxembourg</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G9" s="78"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Germany</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G10" s="78"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austria</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G11" s="78"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Switzerland</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G12" s="78"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liechtenstein</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G13" s="78"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sweden</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-18</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G14" s="78"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denmark</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-18</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G15" s="78"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finland</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-18</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G16" s="78"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iceland</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-18</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G17" s="78"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monaco</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-02</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G18" s="78"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australasia</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-29</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G19" s="78"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australasia</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Zealand</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live</t>
+        </is>
+      </c>
+      <c r="D20" s="42">
+        <v>45293.0</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G20" s="78"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G21" s="78"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italy</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G22" s="78"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poland</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G23" s="78"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andorra</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G24" s="78"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malta</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G25" s="78"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developed Europe</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Marino</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G26" s="78"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mexico</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G27" s="78"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brazil</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D28" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G28" s="78"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colombia</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D29" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G29" s="78"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chile</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D30" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G30" s="78"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peru</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D31" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G31" s="78"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecuador</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D32" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G32" s="78"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolivia</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D33" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G33" s="78"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paraguay</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D34" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G34" s="78"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uruguay</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D35" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G35" s="78"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guyana</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D36" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G36" s="78"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suriname</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D37" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G37" s="78"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costa Rica</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D38" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G38" s="78"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El Salvador</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D39" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G39" s="78"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guatemala</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D40" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G40" s="78"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Honduras</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D41" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G41" s="78"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nicaragua</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D42" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G42" s="78"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panama</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D43" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G43" s="78"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belize</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D44" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G44" s="78"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dominican Republic</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D45" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G45" s="78"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jamaica</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D46" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ad revenue share + Premium video share</t>
+        </is>
+      </c>
+      <c r="G46" s="78"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Bahamas</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D47" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G47" s="78"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barbados</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D48" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G48" s="78"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D49" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G49" s="78"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curaçao</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D50" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G50" s="78"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D51" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G51" s="78"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dominica</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D52" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G52" s="78"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grenada</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D53" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G53" s="78"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haiti</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D54" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G54" s="78"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint Kitts and Nevis</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D55" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G55" s="78"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint Lucia</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D56" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G56" s="78"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latin America</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint Vincent and the Grenadines</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling out Oct 20 2026</t>
+        </is>
+      </c>
+      <c r="D57" s="42">
+        <v>46316.0</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ads served elsewhere + Premium video share</t>
+        </is>
+      </c>
+      <c r="G57" s="78"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emerging Europe</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All markets (Czechia, Romania, Ukraine, Greece, Türkiye, Hungary, etc.)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No SPP, none announced</t>
+        </is>
+      </c>
+      <c r="D58" s="42"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not eligible</t>
+        </is>
+      </c>
+      <c r="G58" s="78">
+        <v>8.6</v>
+      </c>
+      <c r="H58" s="78">
+        <v>111</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Support: Spotify Partner Program (as of 2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All markets (India, Japan, South Korea, Pakistan, Bangladesh, Taiwan, HK, etc.)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No SPP, none announced</t>
+        </is>
+      </c>
+      <c r="D59" s="42"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not eligible</t>
+        </is>
+      </c>
+      <c r="G59" s="78">
+        <v>6.9</v>
+      </c>
+      <c r="H59" s="78">
+        <v>1255</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Support: Spotify Partner Program (as of 2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southeast Asia</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indonesia, Philippines, Malaysia, Singapore, Thailand, Vietnam</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No SPP, none announced</t>
+        </is>
+      </c>
+      <c r="D60" s="42"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not eligible</t>
+        </is>
+      </c>
+      <c r="G60" s="78">
+        <v>6.4</v>
+      </c>
+      <c r="H60" s="78">
+        <v>292</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Support: Spotify Partner Program (as of 2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middle East</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israel, Saudi Arabia, UAE, Qatar, Kuwait, Bahrain, etc.</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No SPP, none announced</t>
+        </is>
+      </c>
+      <c r="D61" s="42"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not eligible</t>
+        </is>
+      </c>
+      <c r="G61" s="78">
+        <v>1.3</v>
+      </c>
+      <c r="H61" s="78">
+        <v>23</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Support: Spotify Partner Program (as of 2026-10-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Africa</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">South Africa, Nigeria, Kenya, Egypt, Ghana, Morocco, etc.</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No SPP, none announced</t>
+        </is>
+      </c>
+      <c r="D62" s="44"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not eligible</t>
+        </is>
+      </c>
+      <c r="G62" s="80">
+        <v>24.2</v>
+      </c>
+      <c r="H62" s="80">
+        <v>278</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Support: Spotify Partner Program (as of 2026-10-15)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>
